--- a/data/trans_bre/P19C05-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P19C05-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,52; 5,63</t>
+          <t>-10,08; 4,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 6,95</t>
+          <t>-6,68; 7,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 7,7</t>
+          <t>-1,86; 7,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 2,15</t>
+          <t>-6,11; 2,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-44,35; 43,28</t>
+          <t>-47,5; 34,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-35,85; 58,1</t>
+          <t>-33,36; 63,05</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-26,73; 249,3</t>
+          <t>-28,3; 250,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-49,09; 29,37</t>
+          <t>-47,57; 29,87</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 4,11</t>
+          <t>-5,39; 4,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 9,06</t>
+          <t>-0,41; 9,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 6,38</t>
+          <t>-4,4; 6,63</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,05; 9,1</t>
+          <t>1,99; 8,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-33,64; 36,54</t>
+          <t>-33,25; 35,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-6,4; 101,62</t>
+          <t>-4,15; 100,56</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-25,82; 58,45</t>
+          <t>-25,3; 60,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>20,84; 158,62</t>
+          <t>21,71; 153,24</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,57; 17,38</t>
+          <t>3,72; 16,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 12,7</t>
+          <t>-0,34; 13,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 3,62</t>
+          <t>-6,22; 3,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 7,86</t>
+          <t>-1,27; 7,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19,88; 165,68</t>
+          <t>19,63; 173,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 91,19</t>
+          <t>-2,3; 95,94</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-45,62; 42,04</t>
+          <t>-46,0; 43,23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,91; 87,76</t>
+          <t>-9,54; 77,56</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,13; 12,53</t>
+          <t>-0,7; 12,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 8,89</t>
+          <t>-1,86; 9,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 8,6</t>
+          <t>-2,18; 9,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,92; 2,69</t>
+          <t>-7,75; 2,62</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,31; 98,03</t>
+          <t>-4,06; 93,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-17,04; 80,13</t>
+          <t>-12,07; 81,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-19,19; 80,2</t>
+          <t>-14,23; 86,27</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-51,55; 25,46</t>
+          <t>-50,22; 26,6</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 11,77</t>
+          <t>-1,07; 11,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,64; 7,99</t>
+          <t>-7,82; 8,64</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,14; 12,01</t>
+          <t>-6,55; 11,06</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,28; 14,67</t>
+          <t>4,43; 14,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-17,46; 198,33</t>
+          <t>-18,05; 189,64</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-36,14; 64,63</t>
+          <t>-36,36; 70,43</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-33,37; 126,43</t>
+          <t>-34,54; 109,27</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>29,79; 177,03</t>
+          <t>29,72; 173,19</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-11,14; 4,06</t>
+          <t>-11,48; 3,7</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,24; 15,3</t>
+          <t>2,06; 15,31</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 3,94</t>
+          <t>-5,34; 3,98</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 2,42</t>
+          <t>-5,35; 2,71</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-48,24; 27,02</t>
+          <t>-49,14; 24,34</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11,18; 172,28</t>
+          <t>14,1; 180,13</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-56,58; 79,08</t>
+          <t>-58,36; 82,01</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-37,49; 23,61</t>
+          <t>-36,16; 28,0</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 4,2</t>
+          <t>-4,97; 4,48</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 6,05</t>
+          <t>-3,77; 5,79</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 4,56</t>
+          <t>-3,18; 4,42</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-10,59; 1,09</t>
+          <t>-9,82; 1,05</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-28,65; 31,96</t>
+          <t>-28,08; 34,87</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-16,74; 35,78</t>
+          <t>-16,96; 33,36</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-30,74; 72,73</t>
+          <t>-31,93; 70,63</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-69,89; 9,44</t>
+          <t>-67,67; 8,46</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,34; 8,48</t>
+          <t>1,33; 8,52</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 6,81</t>
+          <t>-1,18; 6,71</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 3,8</t>
+          <t>-3,54; 3,51</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,27; 7,5</t>
+          <t>0,58; 7,92</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>11,76; 128,38</t>
+          <t>12,76; 121,67</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-11,93; 60,64</t>
+          <t>-8,6; 62,26</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-25,14; 36,16</t>
+          <t>-25,94; 36,19</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,98; 246,43</t>
+          <t>6,17; 265,65</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,54; 4,66</t>
+          <t>0,56; 4,36</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,31; 5,12</t>
+          <t>1,11; 5,31</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 2,85</t>
+          <t>-0,69; 2,71</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 3,67</t>
+          <t>-0,51; 4,06</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,4; 36,38</t>
+          <t>3,47; 34,08</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,77; 36,56</t>
+          <t>6,88; 38,05</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 29,42</t>
+          <t>-6,01; 27,68</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-7,36; 45,11</t>
+          <t>-4,27; 50,58</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P19C05-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P19C05-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-1,72</t>
+          <t>-3,04</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-17,89%</t>
+          <t>-29,11%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,08; 4,97</t>
+          <t>-10,17; 4,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 7,44</t>
+          <t>-6,59; 7,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 7,14</t>
+          <t>-1,4; 7,47</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 2,14</t>
+          <t>-7,18; 0,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-47,5; 34,14</t>
+          <t>-45,3; 29,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-33,36; 63,05</t>
+          <t>-36,67; 66,22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-28,3; 250,47</t>
+          <t>-22,3; 234,72</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-47,57; 29,87</t>
+          <t>-54,94; 10,23</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5,6</t>
+          <t>5,17</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>63,75%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,39; 4,16</t>
+          <t>-6,31; 4,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 9,07</t>
+          <t>-0,21; 9,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 6,63</t>
+          <t>-3,91; 6,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,99; 8,89</t>
+          <t>1,34; 8,5</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-33,25; 35,04</t>
+          <t>-35,46; 34,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 100,56</t>
+          <t>-1,9; 114,04</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-25,3; 60,69</t>
+          <t>-25,09; 62,34</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>21,71; 153,24</t>
+          <t>11,42; 128,06</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,22</t>
+          <t>3,45</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>30,56%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,72; 16,88</t>
+          <t>3,8; 17,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 13,1</t>
+          <t>-0,07; 13,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 3,7</t>
+          <t>-6,51; 3,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 7,13</t>
+          <t>-1,1; 7,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19,63; 173,77</t>
+          <t>20,94; 176,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 95,94</t>
+          <t>-1,98; 93,94</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-46,0; 43,23</t>
+          <t>-47,77; 38,91</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-9,54; 77,56</t>
+          <t>-8,73; 79,53</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-1,9</t>
+          <t>0,81</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-15,62%</t>
+          <t>6,89%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 12,27</t>
+          <t>-0,9; 12,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 9,01</t>
+          <t>-2,78; 8,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 9,03</t>
+          <t>-2,19; 9,48</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,75; 2,62</t>
+          <t>-4,14; 4,75</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 93,23</t>
+          <t>-4,57; 94,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-12,07; 81,99</t>
+          <t>-17,66; 75,11</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-14,23; 86,27</t>
+          <t>-14,98; 91,7</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-50,22; 26,6</t>
+          <t>-27,29; 51,85</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9,89</t>
+          <t>9,75</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>93,13%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 11,27</t>
+          <t>-0,96; 11,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,82; 8,64</t>
+          <t>-8,02; 6,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 11,06</t>
+          <t>-6,31; 11,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,43; 14,78</t>
+          <t>4,83; 14,37</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-18,05; 189,64</t>
+          <t>-11,26; 193,84</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-36,36; 70,43</t>
+          <t>-38,48; 54,81</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-34,54; 109,27</t>
+          <t>-32,99; 126,45</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>29,72; 173,19</t>
+          <t>35,68; 182,18</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-1,56</t>
+          <t>-1,85</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-12,26%</t>
+          <t>-14,33%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-11,48; 3,7</t>
+          <t>-11,15; 3,8</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,06; 15,31</t>
+          <t>2,39; 15,23</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 3,98</t>
+          <t>-5,28; 4,07</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 2,71</t>
+          <t>-6,47; 2,41</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-49,14; 24,34</t>
+          <t>-47,88; 25,22</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14,1; 180,13</t>
+          <t>17,94; 171,15</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-58,36; 82,01</t>
+          <t>-56,78; 83,97</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-36,16; 28,0</t>
+          <t>-40,48; 23,49</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-3,53</t>
+          <t>-0,3</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-28,07%</t>
+          <t>-2,3%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 4,48</t>
+          <t>-5,26; 4,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 5,79</t>
+          <t>-3,88; 5,59</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 4,42</t>
+          <t>-3,22; 4,39</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-9,82; 1,05</t>
+          <t>-4,06; 3,39</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-28,08; 34,87</t>
+          <t>-29,86; 31,16</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-16,96; 33,36</t>
+          <t>-16,62; 32,49</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-31,93; 70,63</t>
+          <t>-31,07; 70,11</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-67,67; 8,46</t>
+          <t>-26,28; 31,04</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3,47</t>
+          <t>1,59</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>57,99%</t>
+          <t>20,4%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,33; 8,52</t>
+          <t>0,95; 8,44</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 6,71</t>
+          <t>-1,13; 6,73</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 3,51</t>
+          <t>-3,48; 3,7</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,58; 7,92</t>
+          <t>-0,82; 3,85</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>12,76; 121,67</t>
+          <t>7,93; 128,97</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-8,6; 62,26</t>
+          <t>-8,01; 61,47</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-25,94; 36,19</t>
+          <t>-25,47; 39,09</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>6,17; 265,65</t>
+          <t>-9,24; 58,19</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1,56</t>
+          <t>1,7</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,38%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,56; 4,36</t>
+          <t>0,46; 4,38</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,11; 5,31</t>
+          <t>1,16; 5,11</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 2,71</t>
+          <t>-0,8; 2,75</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 4,06</t>
+          <t>0,52; 3,18</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,47; 34,08</t>
+          <t>3,27; 35,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,88; 38,05</t>
+          <t>7,72; 37,39</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 27,68</t>
+          <t>-7,01; 28,16</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 50,58</t>
+          <t>4,74; 33,49</t>
         </is>
       </c>
     </row>
